--- a/improvement/realestate/plan-10.xlsx
+++ b/improvement/realestate/plan-10.xlsx
@@ -610,7 +610,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>3/4（賃上げ後の事業場内最低賃金1,000円未満は4/5）</t>
+          <t>3/4（引上げ前の事業場内最低賃金が1,050円未満は4/5）</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>450万円（90円コース・引上げ人数による。特例600万円）</t>
+          <t>コース（50円/70円/90円）と引上げ人数で変動。90円コース・7人以上で450万円</t>
         </is>
       </c>
     </row>
